--- a/public/templates/forms/A-144-FailoverTestRecords-FORM.xlsx
+++ b/public/templates/forms/A-144-FailoverTestRecords-FORM.xlsx
@@ -3,12 +3,15 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="720" yWindow="780" windowWidth="23380" windowHeight="21660" tabRatio="500" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="720" yWindow="780" windowWidth="23380" windowHeight="21660" tabRatio="500" firstSheet="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Log" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Column Instructions" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm.Print_Titles" localSheetId="0">Log!$11:$11</definedName>
+  </definedNames>
   <definedNames/>
   <calcPr calcId="191029" fullCalcOnLoad="1"/>
 </workbook>
@@ -16,7 +19,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
+  </numFmts>
   <fonts count="11">
     <font>
       <name val="Aptos"/>
@@ -187,7 +192,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -242,6 +247,9 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf applyNumberFormat="1" numFmtId="164" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -615,7 +623,7 @@
         </is>
       </c>
     </row>
-    <row r="11" ht="30" customHeight="1">
+    <row r="11" ht="34.7" customHeight="1">
       <c r="A11" s="10" t="inlineStr">
         <is>
           <t>Entry #</t>
@@ -977,7 +985,7 @@
     <mergeCell ref="A25:F25"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1" horizontalDpi="300" verticalDpi="300"/>
+  <pageSetup paperSize="1" orientation="landscape" fitToWidth="1" fitToHeight="0"/>
 </worksheet>
 </file>
 
@@ -1003,14 +1011,14 @@
         </is>
       </c>
     </row>
-    <row r="2" ht="43.5" customHeight="1">
+    <row r="2" ht="50.5" customHeight="1">
       <c r="A2" s="1" t="inlineStr">
         <is>
           <t>How to use this template: replace every [BRACKETED] field with your agency's information and follow the « » guidance notes, then delete every « » note before publishing. This sheet explains each column; it is guidance only and can be removed once the record is populated.</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="29.75" customHeight="1">
+    <row r="3" ht="34.7" customHeight="1">
       <c r="A3" s="8" t="inlineStr">
         <is>
           <t>Placeholder key:  [BRACKETED] = fill in   ·   « » = guidance to delete.  Classification, findings, sign-off, retention and revision history live on the Log tab.</t>
@@ -1084,13 +1092,11 @@
           <t>Required</t>
         </is>
       </c>
-      <c r="D8" s="11" t="inlineStr">
-        <is>
-          <t>2026-04-02</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="30" customHeight="1">
+      <c r="D8" s="22">
+        <v>46114</v>
+      </c>
+    </row>
+    <row r="9" ht="34.7" customHeight="1">
       <c r="A9" s="15" t="inlineStr">
         <is>
           <t>Failover path / component</t>
@@ -1112,7 +1118,7 @@
         </is>
       </c>
     </row>
-    <row r="10" ht="30" customHeight="1">
+    <row r="10" ht="34.7" customHeight="1">
       <c r="A10" s="15" t="inlineStr">
         <is>
           <t>Simulated failure scenario</t>
@@ -1134,7 +1140,7 @@
         </is>
       </c>
     </row>
-    <row r="11" ht="30" customHeight="1">
+    <row r="11" ht="34.7" customHeight="1">
       <c r="A11" s="15" t="inlineStr">
         <is>
           <t>Expected vs actual shift time</t>
@@ -1156,7 +1162,7 @@
         </is>
       </c>
     </row>
-    <row r="12" ht="30" customHeight="1">
+    <row r="12" ht="34.7" customHeight="1">
       <c r="A12" s="15" t="inlineStr">
         <is>
           <t>Result &amp; remediation</t>
@@ -1264,6 +1270,6 @@
     <mergeCell ref="A14:D14"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup orientation="landscape" fitToHeight="0" horizontalDpi="300" verticalDpi="300"/>
+  <pageSetup paperSize="1" orientation="landscape" fitToWidth="1" fitToHeight="0"/>
 </worksheet>
 </file>